--- a/DeskripsiSektor.xlsx
+++ b/DeskripsiSektor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/RegEco-PADAGIMO-SOLUSI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F0CF8D1-6723-42CB-BC9E-2A2E7627ACE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{1F0CF8D1-6723-42CB-BC9E-2A2E7627ACE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0FE027B-A1D4-4410-BF9D-92FCC997EBCF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{1E0A43EB-EC49-42B0-9365-5ED38BF751B7}"/>
   </bookViews>
@@ -18,28 +18,27 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
-    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="Chart_Sektor_name">OFFSET([1]Industri_Unggulan!$B$8,1,1,[1]g!$E$3,1)</definedName>
     <definedName name="Chart_Sektor_x">OFFSET([1]Industri_Unggulan!$F$8,1,1,[1]g!$E$3,1)</definedName>
     <definedName name="Chart_Sektor_y">OFFSET([1]Industri_Unggulan!$E$8,1,1,[1]g!$E$3,1)</definedName>
     <definedName name="cwww10">#REF!</definedName>
-    <definedName name="Industri">[3]K.Supply!$P$2:$P$96</definedName>
-    <definedName name="Kategori">[3]Sheet1!$U$2:$U$18</definedName>
-    <definedName name="Nama_KabKota">[3]Sheet2!$F$2:$F$40</definedName>
-    <definedName name="NamaTabel">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$6"),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="Industri">[2]K.Supply!$P$2:$P$96</definedName>
+    <definedName name="Kategori">[2]Sheet1!$U$2:$U$18</definedName>
+    <definedName name="Nama_KabKota">[2]Sheet2!$F$2:$F$40</definedName>
+    <definedName name="NamaTabel">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$6"),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="NamaTabelImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$6"),0,0,1,#REF!)</definedName>
-    <definedName name="Produk">[3]K.Supply!$T$2:$T$76</definedName>
-    <definedName name="Tabel">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$"&amp;[3]S2LP!$H$1),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="Produk">[2]K.Supply!$T$2:$T$76</definedName>
+    <definedName name="Tabel">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$"&amp;[2]S2LP!$H$1),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$"&amp;#REF!),0,0,1,#REF!)</definedName>
-    <definedName name="TabelKab">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$"&amp;[3]S2LP!$H$2),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="TabelKab">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$"&amp;[2]S2LP!$H$2),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelKabImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$"&amp;#REF!),0,0,1,#REF!)</definedName>
-    <definedName name="TabelKabTotal">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$170"),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="TabelKabTotal">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$170"),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelKabTotalImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$293"),0,0,1,#REF!)</definedName>
-    <definedName name="TabelTotal">OFFSET(INDIRECT("S3R!$"&amp;[3]S2LP!$G$2&amp;"$169"),0,0,1,[3]S2LP!$G$1)</definedName>
+    <definedName name="TabelTotal">OFFSET(INDIRECT("S3R!$"&amp;[2]S2LP!$G$2&amp;"$169"),0,0,1,[2]S2LP!$G$1)</definedName>
     <definedName name="TabelTotalImplisit">OFFSET(INDIRECT("S3R!$"&amp;#REF!&amp;"$292"),0,0,1,#REF!)</definedName>
-    <definedName name="Tahun">[3]Sheet1!$A$2:$A$18</definedName>
+    <definedName name="Tahun">[2]Sheet1!$A$2:$A$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -78,7 +77,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Bodro, Dewi Kiswani:</t>
         </r>
@@ -87,7 +86,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 dummy nilai</t>
@@ -656,13 +655,13 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -841,337 +840,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Tenaga Kerja"/>
-      <sheetName val="KBLI"/>
-      <sheetName val="Laju PDRB atas harga 2010"/>
-      <sheetName val="PDRB growth"/>
-      <sheetName val="LM BAU"/>
-      <sheetName val="LM GBP 2029"/>
-      <sheetName val="LM GBP 2034"/>
-      <sheetName val="LM GBP 2039"/>
-      <sheetName val="LM GBP 2044"/>
-      <sheetName val="LM GBP 2049"/>
-      <sheetName val="LM GBP 2029 B"/>
-      <sheetName val="LM GBP 2034 B"/>
-      <sheetName val="LM GBP 2039 B"/>
-      <sheetName val="LM GBP 2044 B"/>
-      <sheetName val="LM GBP 2049 B"/>
-      <sheetName val="LM GBP Hlr 2029 B"/>
-      <sheetName val="LM GBP Hlr 2034 B"/>
-      <sheetName val="LM GBP Hlr 2039 B"/>
-      <sheetName val="LM GBP Hlr 2044 B"/>
-      <sheetName val="LM GBP Hlr 2049 B"/>
-      <sheetName val="LM GBP 2029 GB"/>
-      <sheetName val="LM GBP 2034 GB"/>
-      <sheetName val="LM GBP 2039 GB"/>
-      <sheetName val="LM GBP 2044 GB"/>
-      <sheetName val="LM GBP 2049 GB"/>
-      <sheetName val="LM GBP Hlr 2029"/>
-      <sheetName val="LM GBP Hlr 2034"/>
-      <sheetName val="LM GBP Hlr 2039"/>
-      <sheetName val="LM GBP Hlr 2044"/>
-      <sheetName val="LM GBP Hlr 2049"/>
-      <sheetName val="LM GBP Hlr 2029 GB"/>
-      <sheetName val="LM GBP Hlr 2034 GB"/>
-      <sheetName val="LM GBP Hlr 2039 GB"/>
-      <sheetName val="LM GBP Hlr 2044 GB"/>
-      <sheetName val="LM GBP Hlr 2049 GB"/>
-      <sheetName val="IM GBP 2029"/>
-      <sheetName val="IM GBP 2034"/>
-      <sheetName val="IM GBP 2039"/>
-      <sheetName val="IM GBP 2044"/>
-      <sheetName val="IM GBP 2049"/>
-      <sheetName val="IM GBP 2029 B"/>
-      <sheetName val="IM GBP 2034 B"/>
-      <sheetName val="IM GBP 2039 B"/>
-      <sheetName val="IM GBP 2044 B"/>
-      <sheetName val="IM GBP 2049 B"/>
-      <sheetName val="IM GBP 2029 GB"/>
-      <sheetName val="IM GBP 2034 GB"/>
-      <sheetName val="IM GBP 2039 GB"/>
-      <sheetName val="IM GBP 2044 GB"/>
-      <sheetName val="IM GBP 2049 GB"/>
-      <sheetName val="IM GBP Hlr 2029"/>
-      <sheetName val="IM GBP Hlr 2034"/>
-      <sheetName val="IM GBP Hlr 2039"/>
-      <sheetName val="IM GBP Hlr 2044"/>
-      <sheetName val="IM GBP Hlr 2049"/>
-      <sheetName val="IM GBP Hlr 2029 B"/>
-      <sheetName val="IM GBP Hlr 2034 B"/>
-      <sheetName val="IM GBP Hlr 2039 B"/>
-      <sheetName val="IM GBP Hlr 2044 B"/>
-      <sheetName val="IM GBP Hlr 2049 B"/>
-      <sheetName val="IM GBP Hlr 2029 GB"/>
-      <sheetName val="IM GBP Hlr 2034 GB"/>
-      <sheetName val="IM GBP Hlr 2039 GB"/>
-      <sheetName val="IM GBP Hlr 2044 GB"/>
-      <sheetName val="IM GBP Hlr 2049 GB"/>
-      <sheetName val="SB BAU"/>
-      <sheetName val="SB GBP 2029"/>
-      <sheetName val="SB GBP 2034"/>
-      <sheetName val="SB GBP 2039"/>
-      <sheetName val="SB GBP 2044"/>
-      <sheetName val="SB GBP 2049"/>
-      <sheetName val="SB GBP Hlr 2029"/>
-      <sheetName val="SB GBP Hlr 2034"/>
-      <sheetName val="SB GBP Hlr 2039"/>
-      <sheetName val="SB GBP Hlr 2044"/>
-      <sheetName val="SB GBP Hlr 2049"/>
-      <sheetName val="SB GBP Hlr 2029 B"/>
-      <sheetName val="SB GBP Hlr 2034 B"/>
-      <sheetName val="SB GBP Hlr 2039 B"/>
-      <sheetName val="SB GBP Hlr 2044 B"/>
-      <sheetName val="SB GBP Hlr 2049 B"/>
-      <sheetName val="SB GBP Hlr 2029 GB"/>
-      <sheetName val="SB GBP Hlr 2034 GB"/>
-      <sheetName val="SB GBP Hlr 2039 GB"/>
-      <sheetName val="SB GBP Hlr 2044 GB"/>
-      <sheetName val="SB GBP Hlr 2049 GB"/>
-      <sheetName val="SB GBP 2029 B"/>
-      <sheetName val="SB GBP 2034 B"/>
-      <sheetName val="SB GBP 2039 B"/>
-      <sheetName val="SB GBP 2044 B"/>
-      <sheetName val="SB GBP 2049 B"/>
-      <sheetName val="SB GBP 2029 GB"/>
-      <sheetName val="SB GBP 2034 GB"/>
-      <sheetName val="SB GBP 2039 GB"/>
-      <sheetName val="SB GBP 2044 GB"/>
-      <sheetName val="SB GBP 2049 GB"/>
-      <sheetName val="IM BAU"/>
-      <sheetName val="Land Productivity"/>
-      <sheetName val="IO_2024_Awal"/>
-      <sheetName val="IO-2024"/>
-      <sheetName val="IO-2029"/>
-      <sheetName val="IO-2029 Prod Test"/>
-      <sheetName val="IO-2034"/>
-      <sheetName val="IO-2039"/>
-      <sheetName val="IO-2044"/>
-      <sheetName val="IO-2049"/>
-      <sheetName val="BAU"/>
-      <sheetName val="Summary BAU"/>
-      <sheetName val="LR_BAU"/>
-      <sheetName val="GGBP"/>
-      <sheetName val="Summary GGBP"/>
-      <sheetName val="LR_GBP"/>
-      <sheetName val="GBP Prod Green"/>
-      <sheetName val="Summary GBP Prod Green"/>
-      <sheetName val="GBP Hlr Green"/>
-      <sheetName val="GBP Prod Blue"/>
-      <sheetName val="Summary GBP Prod Blue"/>
-      <sheetName val="GBP Prod Green-Blue"/>
-      <sheetName val="Summary GBP Prod Green-Blue"/>
-      <sheetName val="Summary GBP Hlr Green"/>
-      <sheetName val="Summary GBP Hlr Blue"/>
-      <sheetName val="GBP Hlr Blue"/>
-      <sheetName val="Summary GBP Hlr Green-Blue"/>
-      <sheetName val="GBP Hlr Green-Blue"/>
-      <sheetName val="IO-2029 HlrG"/>
-      <sheetName val="IO-2034 HlrG"/>
-      <sheetName val="IO-2039 HlrG"/>
-      <sheetName val="IO-2044 HlrG"/>
-      <sheetName val="IO-2049 HlrG"/>
-      <sheetName val="IO-2029 HlrGB"/>
-      <sheetName val="IO-2034 HlrGB"/>
-      <sheetName val="IO-2039 HlrGB"/>
-      <sheetName val="IO-2044 HlrGB"/>
-      <sheetName val="IO-2049 HlrGB"/>
-      <sheetName val="Skenario Hilirisasi"/>
-      <sheetName val="Narasi"/>
-      <sheetName val="IO-2029 HlrB"/>
-      <sheetName val="IO-2034 HlrB"/>
-      <sheetName val="IO-2039 HlrB"/>
-      <sheetName val="IO-2044 HlrB"/>
-      <sheetName val="IO-2049 HlrB"/>
-      <sheetName val="GDP Comparison"/>
-      <sheetName val="Vis GDP"/>
-      <sheetName val="LM Comparison"/>
-      <sheetName val="IM Comparison Pesisir"/>
-      <sheetName val="IM Comparison"/>
-      <sheetName val="Vis Income Pesisir"/>
-      <sheetName val="Vis Income"/>
-      <sheetName val="SUB Comparison"/>
-      <sheetName val="sub  "/>
-      <sheetName val="Rasio SUBIM"/>
-      <sheetName val="Comparison ITBL Linkage"/>
-      <sheetName val="Comparison ITBL Linkage_Vis"/>
-      <sheetName val="Comparison ITFL Linkage"/>
-      <sheetName val="Comparison ITFL Linkage_Vis"/>
-      <sheetName val="Intensitas Emisi"/>
-      <sheetName val="Data Perikanan Darat"/>
-      <sheetName val="Rasio Pendapatan dan KU"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41"/>
-      <sheetData sheetId="42"/>
-      <sheetData sheetId="43"/>
-      <sheetData sheetId="44"/>
-      <sheetData sheetId="45"/>
-      <sheetData sheetId="46"/>
-      <sheetData sheetId="47"/>
-      <sheetData sheetId="48"/>
-      <sheetData sheetId="49"/>
-      <sheetData sheetId="50"/>
-      <sheetData sheetId="51"/>
-      <sheetData sheetId="52"/>
-      <sheetData sheetId="53"/>
-      <sheetData sheetId="54"/>
-      <sheetData sheetId="55"/>
-      <sheetData sheetId="56"/>
-      <sheetData sheetId="57"/>
-      <sheetData sheetId="58"/>
-      <sheetData sheetId="59"/>
-      <sheetData sheetId="60"/>
-      <sheetData sheetId="61"/>
-      <sheetData sheetId="62"/>
-      <sheetData sheetId="63"/>
-      <sheetData sheetId="64"/>
-      <sheetData sheetId="65"/>
-      <sheetData sheetId="66"/>
-      <sheetData sheetId="67"/>
-      <sheetData sheetId="68"/>
-      <sheetData sheetId="69"/>
-      <sheetData sheetId="70"/>
-      <sheetData sheetId="71"/>
-      <sheetData sheetId="72"/>
-      <sheetData sheetId="73"/>
-      <sheetData sheetId="74"/>
-      <sheetData sheetId="75"/>
-      <sheetData sheetId="76"/>
-      <sheetData sheetId="77"/>
-      <sheetData sheetId="78"/>
-      <sheetData sheetId="79"/>
-      <sheetData sheetId="80"/>
-      <sheetData sheetId="81"/>
-      <sheetData sheetId="82"/>
-      <sheetData sheetId="83"/>
-      <sheetData sheetId="84"/>
-      <sheetData sheetId="85"/>
-      <sheetData sheetId="86"/>
-      <sheetData sheetId="87"/>
-      <sheetData sheetId="88"/>
-      <sheetData sheetId="89"/>
-      <sheetData sheetId="90"/>
-      <sheetData sheetId="91"/>
-      <sheetData sheetId="92"/>
-      <sheetData sheetId="93"/>
-      <sheetData sheetId="94"/>
-      <sheetData sheetId="95"/>
-      <sheetData sheetId="96"/>
-      <sheetData sheetId="97"/>
-      <sheetData sheetId="98"/>
-      <sheetData sheetId="99"/>
-      <sheetData sheetId="100"/>
-      <sheetData sheetId="101"/>
-      <sheetData sheetId="102"/>
-      <sheetData sheetId="103"/>
-      <sheetData sheetId="104"/>
-      <sheetData sheetId="105"/>
-      <sheetData sheetId="106"/>
-      <sheetData sheetId="107"/>
-      <sheetData sheetId="108"/>
-      <sheetData sheetId="109"/>
-      <sheetData sheetId="110"/>
-      <sheetData sheetId="111"/>
-      <sheetData sheetId="112"/>
-      <sheetData sheetId="113"/>
-      <sheetData sheetId="114"/>
-      <sheetData sheetId="115"/>
-      <sheetData sheetId="116"/>
-      <sheetData sheetId="117"/>
-      <sheetData sheetId="118"/>
-      <sheetData sheetId="119"/>
-      <sheetData sheetId="120"/>
-      <sheetData sheetId="121"/>
-      <sheetData sheetId="122"/>
-      <sheetData sheetId="123"/>
-      <sheetData sheetId="124"/>
-      <sheetData sheetId="125"/>
-      <sheetData sheetId="126"/>
-      <sheetData sheetId="127"/>
-      <sheetData sheetId="128"/>
-      <sheetData sheetId="129"/>
-      <sheetData sheetId="130"/>
-      <sheetData sheetId="131"/>
-      <sheetData sheetId="132"/>
-      <sheetData sheetId="133"/>
-      <sheetData sheetId="134"/>
-      <sheetData sheetId="135"/>
-      <sheetData sheetId="136"/>
-      <sheetData sheetId="137"/>
-      <sheetData sheetId="138"/>
-      <sheetData sheetId="139"/>
-      <sheetData sheetId="140"/>
-      <sheetData sheetId="141"/>
-      <sheetData sheetId="142"/>
-      <sheetData sheetId="143"/>
-      <sheetData sheetId="144"/>
-      <sheetData sheetId="145"/>
-      <sheetData sheetId="146"/>
-      <sheetData sheetId="147"/>
-      <sheetData sheetId="148"/>
-      <sheetData sheetId="149"/>
-      <sheetData sheetId="150"/>
-      <sheetData sheetId="151"/>
-      <sheetData sheetId="152"/>
-      <sheetData sheetId="153"/>
-      <sheetData sheetId="154"/>
-      <sheetData sheetId="155"/>
-      <sheetData sheetId="156"/>
-      <sheetData sheetId="157"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -2391,13 +2059,13 @@
         <v>11</v>
       </c>
       <c r="F24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>2.6356475098390748E-2</v>
       </c>
       <c r="I24">
         <v>3048</v>
